--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
@@ -1,17 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x15 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="18827"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\aleey\OneDrive\Documents\GitHub\GroupDocs.Assembly-for-Java\Examples\GroupDocs.Assembly.Examples.Java\Data\Storage\Spreadsheet Templates\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11832" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11832" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
-    <sheet name="Evaluation Warning" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
   </sheets>
   <definedNames/>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -21,16 +25,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Evaluation Only. Created with Aspose.Cells for Java.Copyright 2003 - 2016 Aspose Pty Ltd.</t>
-  </si>
-</sst>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -50,25 +50,19 @@
       <color theme="1" tint="0.35"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color theme="1" tint="0.35"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="18"/>
-      <color rgb="FF0000FF"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -83,45 +77,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
+  <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment/>
       <protection/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment/>
-      <protection/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0"/>
-    <cellStyle name="Percent" xfId="15"/>
-    <cellStyle name="Currency" xfId="16"/>
-    <cellStyle name="Currency [0]" xfId="17"/>
-    <cellStyle name="Comma" xfId="18"/>
-    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="3" builtinId="7"/>
+    <cellStyle name="Comma" xfId="4" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="5" builtinId="6"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -219,14 +197,11 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr vert="horz" rot="0"/>
+          <a:bodyPr vert="horz" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" anchor="ctr" anchorCtr="1" wrap="square"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr algn="ctr">
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1400" b="0" i="0" u="none" baseline="0">
+            <a:pPr>
+              <a:defRPr lang="en-US" sz="1400" b="0" i="0" u="none" baseline="0" kern="1200" spc="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
@@ -235,8 +210,10 @@
                 </a:solidFill>
                 <a:latin typeface="Calibri"/>
                 <a:ea typeface="Calibri"/>
-                <a:cs typeface="Calibri"/>
-              </a:rPr>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Total Order Quantity by Quarters</a:t>
             </a:r>
           </a:p>
@@ -275,16 +252,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="3"/>
@@ -335,16 +302,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="3"/>
@@ -395,16 +352,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="3"/>
@@ -455,16 +402,6 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:numFmt formatCode="General" sourceLinked="1"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="0"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-          </c:dLbls>
           <c:cat>
             <c:strLit>
               <c:ptCount val="3"/>
@@ -499,12 +436,21 @@
             </c:ext>
           </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="0"/>
+        </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="82328216"/>
-        <c:axId val="397052433"/>
+        <c:axId val="1529285683"/>
+        <c:axId val="80361763"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="82328216"/>
+        <c:axId val="1529285683"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -528,32 +474,33 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr vert="horz" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" anchor="ctr" anchorCtr="1" wrap="square"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0" kern="1200">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
-                <a:cs typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397052433"/>
+        <c:crossAx val="80361763"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="397052433"/>
+        <c:axId val="80361763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -585,25 +532,26 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr/>
+          <a:bodyPr vert="horz" rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" anchor="ctr" anchorCtr="1" wrap="square"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0">
+              <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0" kern="1200">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Calibri"/>
-                <a:cs typeface="Calibri"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
+            <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82328216"/>
+        <c:crossAx val="1529285683"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -627,22 +575,23 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr vert="horz" rot="0"/>
+        <a:bodyPr vert="horz" rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" anchor="ctr" anchorCtr="1" wrap="square"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
-            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0">
+          <a:pPr algn="l">
+            <a:defRPr lang="en-US" sz="900" b="0" i="0" u="none" baseline="0" kern="1200">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="Calibri"/>
-              <a:ea typeface="Calibri"/>
-              <a:cs typeface="Calibri"/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -665,16 +614,550 @@
     </a:ln>
     <a:effectLst/>
   </c:spPr>
-  <c:txPr>
-    <a:bodyPr vert="horz" rot="0"/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr lang="en-US" u="none" baseline="0"/>
-      </a:pPr>
-    </a:p>
-  </c:txPr>
 </c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -692,14 +1175,20 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
+    <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name="Chart 1"/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="0"/>
-        <a:ext cx="5486400" cy="3200400"/>
+        <a:ext cx="5486400" cy="3048000"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -974,30 +1463,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <dimension ref="A6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="5" ht="23.25" customHeight="1">
-      <c r="A5" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
@@ -446,11 +446,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="1529285683"/>
-        <c:axId val="80361763"/>
+        <c:axId val="453428216"/>
+        <c:axId val="2023948863"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1529285683"/>
+        <c:axId val="453428216"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -493,14 +493,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="80361763"/>
+        <c:crossAx val="2023948863"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="80361763"/>
+        <c:axId val="2023948863"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -551,7 +551,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1529285683"/>
+        <c:crossAx val="453428216"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
@@ -446,11 +446,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="453428216"/>
-        <c:axId val="2023948863"/>
+        <c:axId val="26106704"/>
+        <c:axId val="2047789606"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="453428216"/>
+        <c:axId val="26106704"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -493,14 +493,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2023948863"/>
+        <c:crossAx val="2047789606"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2023948863"/>
+        <c:axId val="2047789606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -551,7 +551,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="453428216"/>
+        <c:crossAx val="26106704"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
+++ b/Examples/GroupDocs.Assembly.Examples.Java/Data/Output/Spreadsheet Reports/Chart with Filtering, Grouping, and Ordering_Dynamic_Title.xlsx
@@ -446,11 +446,11 @@
           <c:showLeaderLines val="0"/>
         </c:dLbls>
         <c:overlap val="100"/>
-        <c:axId val="26106704"/>
         <c:axId val="2047789606"/>
+        <c:axId val="760519665"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="26106704"/>
+        <c:axId val="2047789606"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -493,14 +493,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2047789606"/>
+        <c:crossAx val="760519665"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2047789606"/>
+        <c:axId val="760519665"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -551,7 +551,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26106704"/>
+        <c:crossAx val="2047789606"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
